--- a/survey_templates/028_ai_motion_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/028_ai_motion_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -981,8 +981,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'sports_&amp;_fitness_(e.g.,_yoga,_squats,_golf)',_'value':_'fitness'}</t>
+          <t>sports_&amp;_fitness_(e.g.,_yoga,_squats,_golf)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Sports &amp; Fitness (e.g., Yoga, Squats, Golf)', 'value': 'fitness'}</t>
+          <t>Sports &amp; Fitness (e.g., Yoga, Squats, Golf)</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'physical_rehabilitation_/_therapy',_'value':_'rehab'}</t>
+          <t>physical_rehabilitation_/_therapy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Rehabilitation / Therapy', 'value': 'rehab'}</t>
+          <t>Physical Rehabilitation / Therapy</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'industrial_/_workplace_safety',_'value':_'safety'}</t>
+          <t>industrial_/_workplace_safety</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Industrial / Workplace Safety', 'value': 'safety'}</t>
+          <t>Industrial / Workplace Safety</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'dance_or_creative_performance',_'value':_'creative'}</t>
+          <t>dance_or_creative_performance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Dance or Creative Performance', 'value': 'creative'}</t>
+          <t>Dance or Creative Performance</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'animation_/_cgi_motion_capture',_'value':_'animation'}</t>
+          <t>animation_/_cgi_motion_capture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Animation / CGI Motion Capture', 'value': 'animation'}</t>
+          <t>Animation / CGI Motion Capture</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'standard_smartphone_camera_(front)',_'value':_'smartphone_front'}</t>
+          <t>standard_smartphone_camera_(front)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Smartphone Camera (Front)', 'value': 'smartphone_front'}</t>
+          <t>Standard Smartphone Camera (Front)</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'standard_smartphone_camera_(rear)',_'value':_'smartphone_rear'}</t>
+          <t>standard_smartphone_camera_(rear)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Smartphone Camera (Rear)', 'value': 'smartphone_rear'}</t>
+          <t>Standard Smartphone Camera (Rear)</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'laptop_webcam',_'value':_'webcam'}</t>
+          <t>laptop_webcam</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Laptop Webcam', 'value': 'webcam'}</t>
+          <t>Laptop Webcam</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dedicated_depth_camera_(e.g.,_azure_kinect)',_'value':_'depth_camera'}</t>
+          <t>dedicated_depth_camera_(e.g.,_azure_kinect)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dedicated Depth Camera (e.g., Azure Kinect)', 'value': 'depth_camera'}</t>
+          <t>Dedicated Depth Camera (e.g., Azure Kinect)</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'wearable_inertial_sensors',_'value':_'wearables'}</t>
+          <t>wearable_inertial_sensors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Wearable Inertial Sensors', 'value': 'wearables'}</t>
+          <t>Wearable Inertial Sensors</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'seamless_(no_noticeable_lag)',_'value':_'seamless'}</t>
+          <t>seamless_(no_noticeable_lag)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Seamless (No noticeable lag)', 'value': 'seamless'}</t>
+          <t>Seamless (No noticeable lag)</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'acceptable_(minor_delay,_still_usable)',_'value':_'minor_lag'}</t>
+          <t>acceptable_(minor_delay,_still_usable)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Acceptable (Minor delay, still usable)', 'value': 'minor_lag'}</t>
+          <t>Acceptable (Minor delay, still usable)</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'poor_(significant_delay,_hindered_movement)',_'value':_'high_lag'}</t>
+          <t>poor_(significant_delay,_hindered_movement)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Poor (Significant delay, hindered movement)', 'value': 'high_lag'}</t>
+          <t>Poor (Significant delay, hindered movement)</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'excellent_(very_clear_and_actionable)',_'value':_'excellent'}</t>
+          <t>excellent_(very_clear_and_actionable)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent (Very clear and actionable)', 'value': 'excellent'}</t>
+          <t>Excellent (Very clear and actionable)</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'good_(mostly_clear)',_'value':_'good'}</t>
+          <t>good_(mostly_clear)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Good (Mostly clear)', 'value': 'good'}</t>
+          <t>Good (Mostly clear)</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'neutral_(sometimes_confusing)',_'value':_'neutral'}</t>
+          <t>neutral_(sometimes_confusing)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral (Sometimes confusing)', 'value': 'neutral'}</t>
+          <t>Neutral (Sometimes confusing)</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'poor_(incorrect_or_unhelpful_advice)',_'value':_'poor'}</t>
+          <t>poor_(incorrect_or_unhelpful_advice)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Poor (Incorrect or unhelpful advice)', 'value': 'poor'}</t>
+          <t>Poor (Incorrect or unhelpful advice)</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_completely',_'value':_true}</t>
+          <t>yes,_completely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, completely', 'value': True}</t>
+          <t>Yes, completely</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat', 'value': 'somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_false}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': False}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'more_valuable_(convenient/objective)',_'value':_'more_valuable'}</t>
+          <t>more_valuable_(convenient/objective)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'More Valuable (Convenient/Objective)', 'value': 'more_valuable'}</t>
+          <t>More Valuable (Convenient/Objective)</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'equal_value',_'value':_'equal'}</t>
+          <t>equal_value</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Equal Value', 'value': 'equal'}</t>
+          <t>Equal Value</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'less_valuable_(misses_human_nuance)',_'value':_'less_valuable'}</t>
+          <t>less_valuable_(misses_human_nuance)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Less Valuable (Misses human nuance)', 'value': 'less_valuable'}</t>
+          <t>Less Valuable (Misses human nuance)</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'different_(great_for_drills,_bad_for_strategy)',_'value':_'different'}</t>
+          <t>different_(great_for_drills,_bad_for_strategy)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Different (Great for drills, bad for strategy)', 'value': 'different'}</t>
+          <t>Different (Great for drills, bad for strategy)</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'calibration_failures',_'value':_'calibration'}</t>
+          <t>calibration_failures</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Calibration Failures', 'value': 'calibration'}</t>
+          <t>Calibration Failures</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'poor_lighting_warnings',_'value':_'lighting'}</t>
+          <t>poor_lighting_warnings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Poor Lighting Warnings', 'value': 'lighting'}</t>
+          <t>Poor Lighting Warnings</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'app_crashes_/_freezes',_'value':_'crashes'}</t>
+          <t>app_crashes_/_freezes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'App Crashes / Freezes', 'value': 'crashes'}</t>
+          <t>App Crashes / Freezes</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'connectivity_issues',_'value':_'connectivity'}</t>
+          <t>connectivity_issues</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Connectivity Issues', 'value': 'connectivity'}</t>
+          <t>Connectivity Issues</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent',_'value':_true}</t>
+          <t>yes,_i_consent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent', 'value': True}</t>
+          <t>Yes, I consent</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'no,_please_delete_my_data_after_this_trial',_'value':_false}</t>
+          <t>no,_please_delete_my_data_after_this_trial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'No, please delete my data after this trial', 'value': False}</t>
+          <t>No, please delete my data after this trial</t>
         </is>
       </c>
     </row>
